--- a/2026/2026.xlsx
+++ b/2026/2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
   <si>
     <t>2026年备选游戏列表</t>
   </si>
@@ -104,6 +104,15 @@
     <t>仁王3（新）</t>
   </si>
   <si>
+    <t>已白金，二周目没打</t>
+  </si>
+  <si>
+    <t>2月</t>
+  </si>
+  <si>
+    <t>看9月和27年2月dlc情况决定打几周目，目前封盘</t>
+  </si>
+  <si>
     <t>识质存在（新）</t>
   </si>
   <si>
@@ -152,7 +161,10 @@
     <t>渎神2</t>
   </si>
   <si>
-    <t>2月</t>
+    <t>渎神1</t>
+  </si>
+  <si>
+    <t>战神-斯巴达之子</t>
   </si>
   <si>
     <t>血污夜之仪式</t>
@@ -828,9 +840,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1360,363 +1375,388 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="36.6666666666667" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="16384" width="36.6666666666667" customWidth="1"/>
+    <col min="1" max="16384" width="36.6666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="B29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="30" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="31" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="32" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="33" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="B34" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="35" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/2026/2026.xlsx
+++ b/2026/2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27948" windowHeight="12275"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>2026年备选游戏列表</t>
   </si>
@@ -125,6 +125,9 @@
     <t>明末渊虚之羽</t>
   </si>
   <si>
+    <t>3月</t>
+  </si>
+  <si>
     <t>刺客信条幻景</t>
   </si>
   <si>
@@ -168,6 +171,9 @@
   </si>
   <si>
     <t>血污夜之仪式</t>
+  </si>
+  <si>
+    <t>全收集/全地图二周目通关，斩月模式没打</t>
   </si>
   <si>
     <t>少女与学院城（新）</t>
@@ -840,12 +846,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1382,54 +1385,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1437,32 +1440,32 @@
       </c>
     </row>
     <row r="6" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1470,27 +1473,27 @@
       </c>
     </row>
     <row r="9" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1504,97 +1507,100 @@
       </c>
     </row>
     <row r="11" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>7</v>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>34</v>
+      <c r="E15" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="18" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>38</v>
+      <c r="A18" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="19" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A19" s="2" t="s">
-        <v>40</v>
+      <c r="A19" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1602,16 +1608,16 @@
       </c>
     </row>
     <row r="21" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1619,16 +1625,16 @@
       </c>
     </row>
     <row r="22" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1636,127 +1642,145 @@
       </c>
     </row>
     <row r="23" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>7</v>
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>9</v>
+      <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
+      <c r="A25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="26" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A28" s="2" t="s">
-        <v>49</v>
+      <c r="A28" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>52</v>
+      <c r="A29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>54</v>
+      <c r="A30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A31" s="2" t="s">
-        <v>55</v>
+      <c r="A31" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="32" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>57</v>
+      <c r="A32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="33" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="A33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="E33" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="34" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A34" s="2" t="s">
-        <v>60</v>
+      <c r="A34" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" ht="47.2" customHeight="1" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="36" ht="47.2" customHeight="1" spans="1:5">
-      <c r="A36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
